--- a/MGMP543/Week5RegressionExamples.xlsx
+++ b/MGMP543/Week5RegressionExamples.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gk/Dropbox/rice/teaching/Core Finance Evening MBA 2024-25 Spring (MGMP 543)/slides/Week5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFBA353B-DA59-0145-8756-7E04E1A94993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EF54DDD-CC7E-164F-9F22-72A7E243B5CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-36700" yWindow="-3100" windowWidth="19340" windowHeight="20040" xr2:uid="{271D9179-762E-014F-908A-50691E89DFAD}"/>
+    <workbookView xWindow="-36700" yWindow="-3100" windowWidth="19340" windowHeight="20040" activeTab="1" xr2:uid="{271D9179-762E-014F-908A-50691E89DFAD}"/>
   </bookViews>
   <sheets>
     <sheet name="W4ExampleQ2" sheetId="16" r:id="rId1"/>
@@ -177,9 +177,6 @@
     <t>X Variable 1</t>
   </si>
   <si>
-    <t>1. Data -&gt; Analysis Tools -&gt; Ensure that Analysis ToolPak is ticked</t>
-  </si>
-  <si>
     <t>2. Data -&gt; Data Analysis -&gt; Regression -&gt; Highlight cells for outcome variable (Y) and input variable (X).</t>
   </si>
   <si>
@@ -217,6 +214,9 @@
   </si>
   <si>
     <t>Regression Slope</t>
+  </si>
+  <si>
+    <t>1. (on Mac) Data -&gt; Analysis Tools -&gt; Ensure that Analysis ToolPak is ticked. (on PC) File -&gt; Option -&gt; Add-in -&gt; Analysis ToolPak -&gt; Go -&gt; Select AnalysisToolPak</t>
   </si>
 </sst>
 </file>
@@ -1878,7 +1878,7 @@
         <v>14.432237372739976</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
@@ -1977,7 +1977,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -1985,7 +1985,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -2008,7 +2008,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -2025,37 +2025,37 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -2296,10 +2296,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -2377,10 +2377,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G1" s="9"/>
     </row>
@@ -2441,7 +2441,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -2632,7 +2632,7 @@
     </row>
     <row r="28" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B28" s="3">
         <v>1.5870307167235487</v>

--- a/MGMP543/Week5RegressionExamples.xlsx
+++ b/MGMP543/Week5RegressionExamples.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gk/Dropbox/rice/teaching/Core Finance Evening MBA 2024-25 Spring (MGMP 543)/slides/Week5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EF54DDD-CC7E-164F-9F22-72A7E243B5CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04CC52EE-1E8B-2348-BB89-265458137239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-36700" yWindow="-3100" windowWidth="19340" windowHeight="20040" activeTab="1" xr2:uid="{271D9179-762E-014F-908A-50691E89DFAD}"/>
+    <workbookView xWindow="-36700" yWindow="-3100" windowWidth="19340" windowHeight="20040" xr2:uid="{271D9179-762E-014F-908A-50691E89DFAD}"/>
   </bookViews>
   <sheets>
     <sheet name="W4ExampleQ2" sheetId="16" r:id="rId1"/>
-    <sheet name="W5ExampleSolution" sheetId="7" r:id="rId2"/>
-    <sheet name="W5ExampleRegression" sheetId="11" r:id="rId3"/>
+    <sheet name="W4ExampleQ2Solution" sheetId="7" r:id="rId2"/>
+    <sheet name="W4ExampleQ2Regression" sheetId="11" r:id="rId3"/>
     <sheet name="W5ExampleQ6" sheetId="15" r:id="rId4"/>
     <sheet name="W5ExampleQ6Solution" sheetId="12" r:id="rId5"/>
   </sheets>
